--- a/data/Survey on Engineering Practices for LLM-Based Systems(1-21).xlsx
+++ b/data/Survey on Engineering Practices for LLM-Based Systems(1-21).xlsx
@@ -3255,7 +3255,7 @@
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <x:tableParts count="1">
-    <x:tablePart r:id="Rf30e59bc7b8b4311"/>
+    <x:tablePart r:id="Rcc48dbb3b215485e"/>
   </x:tableParts>
 </x:worksheet>
 </file>